--- a/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/importTecMae.xlsx
+++ b/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/importTecMae.xlsx
@@ -50,12 +50,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="4">
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="yyyy/m/d;@"/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -73,6 +72,21 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
@@ -80,8 +94,39 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -95,108 +140,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -210,8 +156,61 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -232,43 +231,163 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -286,133 +405,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -450,15 +449,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -475,6 +465,30 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
@@ -485,21 +499,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -521,15 +520,6 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -538,157 +528,166 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="26" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -697,9 +696,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1031,29 +1027,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="17.6" outlineLevelRow="7" outlineLevelCol="4"/>
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="17.6" outlineLevelRow="7" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="11" style="1"/>
     <col min="2" max="2" width="18.0583333333333" style="2" customWidth="1"/>
     <col min="3" max="3" width="15.5583333333333" style="2" customWidth="1"/>
-    <col min="5" max="5" width="25" style="3" customWidth="1"/>
-    <col min="8" max="8" width="20.825" customWidth="1"/>
-    <col min="10" max="10" width="23.4666666666667" customWidth="1"/>
-    <col min="12" max="12" width="25.2666666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" spans="1:5">
-      <c r="A1" s="4" t="s">
+    <row r="1" ht="18" spans="1:3">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E1"/>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
@@ -1091,12 +1082,6 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E1048576">
-      <formula1>25569</formula1>
-      <formula2>401769</formula2>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>

--- a/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/importTecMae.xlsx
+++ b/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/importTecMae.xlsx
@@ -16,7 +16,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
-    <t>序号</t>
+    <t>编号</t>
   </si>
   <si>
     <t>技术资料分类</t>
@@ -52,9 +52,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -67,6 +67,142 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -79,142 +215,6 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="34">
     <fill>
@@ -231,181 +231,181 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -449,17 +449,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -484,6 +478,32 @@
       <top/>
       <bottom style="medium">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -517,149 +537,129 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -668,19 +668,19 @@
     <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
